--- a/request_forms/021_lost_luggage_recovery_request_form--request_forms.xlsx
+++ b/request_forms/021_lost_luggage_recovery_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'mr',_'value':_'male'}</t>
+          <t>mr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Mr', 'value': 'Male'}</t>
+          <t>Mr</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'mrs',_'value':_'female'}</t>
+          <t>mrs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Mrs', 'value': 'Female'}</t>
+          <t>Mrs</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
